--- a/LoanOfficer-A/2023/130 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/130 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11900</v>
+        <v>10700</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -894,9 +894,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4">
+        <v>100</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -920,9 +926,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4">
+        <v>100</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -946,9 +958,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4">
+        <v>100</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -972,9 +990,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4">
+        <v>100</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -998,9 +1022,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45894</v>
+      </c>
+      <c r="C8" s="4">
+        <v>100</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1024,9 +1054,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45894</v>
+      </c>
+      <c r="C9" s="4">
+        <v>100</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1050,9 +1086,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45894</v>
+      </c>
+      <c r="C10" s="4">
+        <v>100</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1076,9 +1118,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45894</v>
+      </c>
+      <c r="C11" s="4">
+        <v>100</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1102,9 +1150,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45894</v>
+      </c>
+      <c r="C12" s="4">
+        <v>100</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1128,9 +1182,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45894</v>
+      </c>
+      <c r="C13" s="4">
+        <v>100</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1154,9 +1214,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45894</v>
+      </c>
+      <c r="C14" s="4">
+        <v>100</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1180,9 +1246,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45894</v>
+      </c>
+      <c r="C15" s="4">
+        <v>100</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>

--- a/LoanOfficer-A/2023/130 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/130 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1300</v>
+        <v>4700</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>10700</v>
+        <v>7300</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -874,9 +874,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45914</v>
+      </c>
+      <c r="G3" s="4">
+        <v>100</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -906,9 +912,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45914</v>
+      </c>
+      <c r="G4" s="4">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -938,9 +950,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45921</v>
+      </c>
+      <c r="G5" s="4">
+        <v>100</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -970,9 +988,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45921</v>
+      </c>
+      <c r="G6" s="4">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1002,9 +1026,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45921</v>
+      </c>
+      <c r="G7" s="4">
+        <v>100</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1034,9 +1064,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45921</v>
+      </c>
+      <c r="G8" s="4">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1066,9 +1102,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45921</v>
+      </c>
+      <c r="G9" s="4">
+        <v>100</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1098,9 +1140,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45921</v>
+      </c>
+      <c r="G10" s="4">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1130,9 +1178,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45921</v>
+      </c>
+      <c r="G11" s="4">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1162,9 +1216,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45928</v>
+      </c>
+      <c r="G12" s="4">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1194,9 +1254,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45928</v>
+      </c>
+      <c r="G13" s="4">
+        <v>100</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1226,9 +1292,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45928</v>
+      </c>
+      <c r="G14" s="4">
+        <v>100</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1258,9 +1330,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45928</v>
+      </c>
+      <c r="G15" s="4">
+        <v>100</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1278,15 +1356,27 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45901</v>
+      </c>
+      <c r="C16" s="4">
+        <v>100</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45928</v>
+      </c>
+      <c r="G16" s="4">
+        <v>100</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1304,15 +1394,27 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45901</v>
+      </c>
+      <c r="C17" s="4">
+        <v>100</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45928</v>
+      </c>
+      <c r="G17" s="4">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1330,15 +1432,27 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45901</v>
+      </c>
+      <c r="C18" s="4">
+        <v>100</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45928</v>
+      </c>
+      <c r="G18" s="4">
+        <v>100</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1356,15 +1470,27 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45901</v>
+      </c>
+      <c r="C19" s="4">
+        <v>100</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45928</v>
+      </c>
+      <c r="G19" s="4">
+        <v>100</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1382,9 +1508,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45901</v>
+      </c>
+      <c r="C20" s="4">
+        <v>100</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1408,9 +1540,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45901</v>
+      </c>
+      <c r="C21" s="4">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1434,9 +1572,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45901</v>
+      </c>
+      <c r="C22" s="4">
+        <v>100</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1460,9 +1604,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45910</v>
+      </c>
+      <c r="C23" s="4">
+        <v>100</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1486,9 +1636,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45910</v>
+      </c>
+      <c r="C24" s="4">
+        <v>100</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1512,9 +1668,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45910</v>
+      </c>
+      <c r="C25" s="4">
+        <v>100</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1538,9 +1700,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45910</v>
+      </c>
+      <c r="C26" s="4">
+        <v>100</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1564,9 +1732,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45910</v>
+      </c>
+      <c r="C27" s="4">
+        <v>100</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1590,9 +1764,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45910</v>
+      </c>
+      <c r="C28" s="4">
+        <v>100</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1616,9 +1796,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45910</v>
+      </c>
+      <c r="C29" s="4">
+        <v>100</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1642,9 +1828,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45914</v>
+      </c>
+      <c r="C30" s="4">
+        <v>100</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1668,9 +1860,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45914</v>
+      </c>
+      <c r="C31" s="4">
+        <v>100</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1694,9 +1892,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45914</v>
+      </c>
+      <c r="C32" s="4">
+        <v>100</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/130 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/130 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4700</v>
+        <v>6100</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>7300</v>
+        <v>5900</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45933</v>
+      </c>
+      <c r="K3" s="4">
+        <v>100</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -1520,9 +1526,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G20" s="4">
+        <v>100</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1552,9 +1564,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G21" s="4">
+        <v>100</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1584,9 +1602,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G22" s="4">
+        <v>100</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1616,9 +1640,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G23" s="4">
+        <v>100</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1648,9 +1678,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G24" s="4">
+        <v>100</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1680,9 +1716,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G25" s="4">
+        <v>100</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1712,9 +1754,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G26" s="4">
+        <v>100</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1744,9 +1792,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G27" s="4">
+        <v>100</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1776,9 +1830,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G28" s="4">
+        <v>100</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1808,9 +1868,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G29" s="4">
+        <v>100</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1840,9 +1906,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G30" s="4">
+        <v>100</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1872,9 +1944,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G31" s="4">
+        <v>100</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1904,9 +1982,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45933</v>
+      </c>
+      <c r="G32" s="4">
+        <v>100</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>

--- a/LoanOfficer-A/2023/130 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/130 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>6100</v>
+        <v>6400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5900</v>
+        <v>5600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -930,9 +930,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45947</v>
+      </c>
+      <c r="K4" s="4">
+        <v>100</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -968,9 +974,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>45947</v>
+      </c>
+      <c r="K5" s="4">
+        <v>100</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
@@ -1006,9 +1018,15 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>45947</v>
+      </c>
+      <c r="K6" s="4">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>

--- a/LoanOfficer-A/2023/130 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/130 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>6400</v>
+        <v>9500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5600</v>
+        <v>2500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -898,9 +898,15 @@
       <c r="M3" s="1">
         <v>91</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="1"/>
+      <c r="N3" s="3">
+        <v>45975</v>
+      </c>
+      <c r="O3" s="4">
+        <v>100</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -942,9 +948,15 @@
       <c r="M4" s="1">
         <v>92</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
+      <c r="N4" s="3">
+        <v>45975</v>
+      </c>
+      <c r="O4" s="4">
+        <v>100</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -986,9 +998,15 @@
       <c r="M5" s="1">
         <v>93</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="1"/>
+      <c r="N5" s="3">
+        <v>45975</v>
+      </c>
+      <c r="O5" s="4">
+        <v>100</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1030,9 +1048,15 @@
       <c r="M6" s="1">
         <v>94</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="1"/>
+      <c r="N6" s="3">
+        <v>45975</v>
+      </c>
+      <c r="O6" s="4">
+        <v>100</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1062,15 +1086,27 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>45957</v>
+      </c>
+      <c r="K7" s="4">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="1"/>
+      <c r="N7" s="3">
+        <v>45975</v>
+      </c>
+      <c r="O7" s="4">
+        <v>100</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1100,9 +1136,15 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>45957</v>
+      </c>
+      <c r="K8" s="4">
+        <v>100</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
@@ -1138,9 +1180,15 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>45957</v>
+      </c>
+      <c r="K9" s="4">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
@@ -1176,9 +1224,15 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>45957</v>
+      </c>
+      <c r="K10" s="4">
+        <v>100</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>
@@ -1214,9 +1268,15 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>45957</v>
+      </c>
+      <c r="K11" s="4">
+        <v>100</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>
@@ -1252,9 +1312,15 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>45959</v>
+      </c>
+      <c r="K12" s="4">
+        <v>100</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
@@ -1290,9 +1356,15 @@
       <c r="I13" s="1">
         <v>71</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>45959</v>
+      </c>
+      <c r="K13" s="4">
+        <v>100</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
       <c r="M13" s="1">
         <v>101</v>
       </c>
@@ -1328,9 +1400,15 @@
       <c r="I14" s="1">
         <v>72</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="3">
+        <v>45959</v>
+      </c>
+      <c r="K14" s="4">
+        <v>100</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
       <c r="M14" s="1">
         <v>102</v>
       </c>
@@ -1366,9 +1444,15 @@
       <c r="I15" s="1">
         <v>73</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="3">
+        <v>45959</v>
+      </c>
+      <c r="K15" s="4">
+        <v>100</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
       <c r="M15" s="1">
         <v>103</v>
       </c>
@@ -1404,9 +1488,15 @@
       <c r="I16" s="1">
         <v>74</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="3">
+        <v>45959</v>
+      </c>
+      <c r="K16" s="4">
+        <v>100</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
       <c r="M16" s="1">
         <v>104</v>
       </c>
@@ -1442,9 +1532,15 @@
       <c r="I17" s="1">
         <v>75</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="3">
+        <v>45959</v>
+      </c>
+      <c r="K17" s="4">
+        <v>100</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
       <c r="M17" s="1">
         <v>105</v>
       </c>
@@ -1480,9 +1576,15 @@
       <c r="I18" s="1">
         <v>76</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>45959</v>
+      </c>
+      <c r="K18" s="4">
+        <v>100</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
       <c r="M18" s="1">
         <v>106</v>
       </c>
@@ -1518,9 +1620,15 @@
       <c r="I19" s="1">
         <v>77</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="3">
+        <v>45959</v>
+      </c>
+      <c r="K19" s="4">
+        <v>100</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
@@ -1556,9 +1664,15 @@
       <c r="I20" s="1">
         <v>78</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="3">
+        <v>45959</v>
+      </c>
+      <c r="K20" s="4">
+        <v>100</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
       <c r="M20" s="1">
         <v>108</v>
       </c>
@@ -1594,9 +1708,15 @@
       <c r="I21" s="1">
         <v>79</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
+      <c r="J21" s="3">
+        <v>45961</v>
+      </c>
+      <c r="K21" s="4">
+        <v>100</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
       <c r="M21" s="1">
         <v>109</v>
       </c>
@@ -1632,9 +1752,15 @@
       <c r="I22" s="1">
         <v>80</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
+      <c r="J22" s="3">
+        <v>45961</v>
+      </c>
+      <c r="K22" s="4">
+        <v>100</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
       <c r="M22" s="1">
         <v>110</v>
       </c>
@@ -1670,9 +1796,15 @@
       <c r="I23" s="1">
         <v>81</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
+      <c r="J23" s="3">
+        <v>45961</v>
+      </c>
+      <c r="K23" s="4">
+        <v>100</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
       <c r="M23" s="1">
         <v>111</v>
       </c>
@@ -1708,9 +1840,15 @@
       <c r="I24" s="1">
         <v>82</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
+      <c r="J24" s="3">
+        <v>45961</v>
+      </c>
+      <c r="K24" s="4">
+        <v>100</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
       <c r="M24" s="1">
         <v>112</v>
       </c>
@@ -1746,9 +1884,15 @@
       <c r="I25" s="1">
         <v>83</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
+      <c r="J25" s="3">
+        <v>45966</v>
+      </c>
+      <c r="K25" s="4">
+        <v>100</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
       <c r="M25" s="1">
         <v>113</v>
       </c>
@@ -1784,9 +1928,15 @@
       <c r="I26" s="1">
         <v>84</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
+      <c r="J26" s="3">
+        <v>45966</v>
+      </c>
+      <c r="K26" s="4">
+        <v>100</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
       <c r="M26" s="1">
         <v>114</v>
       </c>
@@ -1822,9 +1972,15 @@
       <c r="I27" s="1">
         <v>85</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
+      <c r="J27" s="3">
+        <v>45966</v>
+      </c>
+      <c r="K27" s="4">
+        <v>100</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
       <c r="M27" s="1">
         <v>115</v>
       </c>
@@ -1860,9 +2016,15 @@
       <c r="I28" s="1">
         <v>86</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="1"/>
+      <c r="J28" s="3">
+        <v>45966</v>
+      </c>
+      <c r="K28" s="4">
+        <v>100</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
       <c r="M28" s="1">
         <v>116</v>
       </c>
@@ -1898,9 +2060,15 @@
       <c r="I29" s="1">
         <v>87</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="1"/>
+      <c r="J29" s="3">
+        <v>45966</v>
+      </c>
+      <c r="K29" s="4">
+        <v>100</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
       <c r="M29" s="1">
         <v>117</v>
       </c>
@@ -1936,9 +2104,15 @@
       <c r="I30" s="1">
         <v>88</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="3">
+        <v>45966</v>
+      </c>
+      <c r="K30" s="4">
+        <v>100</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
       <c r="M30" s="1">
         <v>118</v>
       </c>
@@ -1974,9 +2148,15 @@
       <c r="I31" s="1">
         <v>89</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="J31" s="3">
+        <v>45975</v>
+      </c>
+      <c r="K31" s="4">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="1">
         <v>119</v>
       </c>
@@ -2012,9 +2192,15 @@
       <c r="I32" s="1">
         <v>90</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="J32" s="3">
+        <v>45975</v>
+      </c>
+      <c r="K32" s="4">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
       <c r="M32" s="1">
         <v>120</v>
       </c>

--- a/LoanOfficer-A/2023/130 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/130 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9500</v>
+        <v>10400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>2500</v>
+        <v>1600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1148,9 +1148,15 @@
       <c r="M8" s="1">
         <v>96</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="1"/>
+      <c r="N8" s="3">
+        <v>45981</v>
+      </c>
+      <c r="O8" s="4">
+        <v>100</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1192,9 +1198,15 @@
       <c r="M9" s="1">
         <v>97</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="1"/>
+      <c r="N9" s="3">
+        <v>45981</v>
+      </c>
+      <c r="O9" s="4">
+        <v>100</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1236,9 +1248,15 @@
       <c r="M10" s="1">
         <v>98</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="1"/>
+      <c r="N10" s="3">
+        <v>45981</v>
+      </c>
+      <c r="O10" s="4">
+        <v>100</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1280,9 +1298,15 @@
       <c r="M11" s="1">
         <v>99</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="1"/>
+      <c r="N11" s="3">
+        <v>45983</v>
+      </c>
+      <c r="O11" s="4">
+        <v>100</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1324,9 +1348,15 @@
       <c r="M12" s="1">
         <v>100</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="1"/>
+      <c r="N12" s="3">
+        <v>45983</v>
+      </c>
+      <c r="O12" s="4">
+        <v>100</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1368,9 +1398,15 @@
       <c r="M13" s="1">
         <v>101</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="1"/>
+      <c r="N13" s="3">
+        <v>45983</v>
+      </c>
+      <c r="O13" s="4">
+        <v>100</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1412,9 +1448,15 @@
       <c r="M14" s="1">
         <v>102</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="1"/>
+      <c r="N14" s="3">
+        <v>45983</v>
+      </c>
+      <c r="O14" s="4">
+        <v>100</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1456,9 +1498,15 @@
       <c r="M15" s="1">
         <v>103</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="1"/>
+      <c r="N15" s="3">
+        <v>45985</v>
+      </c>
+      <c r="O15" s="4">
+        <v>100</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -1500,9 +1548,15 @@
       <c r="M16" s="1">
         <v>104</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="1"/>
+      <c r="N16" s="3">
+        <v>45985</v>
+      </c>
+      <c r="O16" s="4">
+        <v>100</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">

--- a/LoanOfficer-A/2023/130 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/130 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>10400</v>
+        <v>11800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>1600</v>
+        <v>200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1598,9 +1598,15 @@
       <c r="M17" s="1">
         <v>105</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="1"/>
+      <c r="N17" s="3">
+        <v>45991</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -1642,9 +1648,15 @@
       <c r="M18" s="1">
         <v>106</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="1"/>
+      <c r="N18" s="3">
+        <v>45991</v>
+      </c>
+      <c r="O18" s="4">
+        <v>100</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1686,9 +1698,15 @@
       <c r="M19" s="1">
         <v>107</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="1"/>
+      <c r="N19" s="3">
+        <v>45991</v>
+      </c>
+      <c r="O19" s="4">
+        <v>100</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -1730,9 +1748,15 @@
       <c r="M20" s="1">
         <v>108</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="1"/>
+      <c r="N20" s="3">
+        <v>45991</v>
+      </c>
+      <c r="O20" s="4">
+        <v>100</v>
+      </c>
+      <c r="P20" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -1774,9 +1798,15 @@
       <c r="M21" s="1">
         <v>109</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="1"/>
+      <c r="N21" s="3">
+        <v>45991</v>
+      </c>
+      <c r="O21" s="4">
+        <v>100</v>
+      </c>
+      <c r="P21" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1818,9 +1848,15 @@
       <c r="M22" s="1">
         <v>110</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="1"/>
+      <c r="N22" s="3">
+        <v>45997</v>
+      </c>
+      <c r="O22" s="4">
+        <v>100</v>
+      </c>
+      <c r="P22" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -1862,9 +1898,15 @@
       <c r="M23" s="1">
         <v>111</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="1"/>
+      <c r="N23" s="3">
+        <v>45997</v>
+      </c>
+      <c r="O23" s="4">
+        <v>100</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1906,9 +1948,15 @@
       <c r="M24" s="1">
         <v>112</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="1"/>
+      <c r="N24" s="3">
+        <v>45997</v>
+      </c>
+      <c r="O24" s="4">
+        <v>100</v>
+      </c>
+      <c r="P24" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -1950,9 +1998,15 @@
       <c r="M25" s="1">
         <v>113</v>
       </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="1"/>
+      <c r="N25" s="3">
+        <v>45997</v>
+      </c>
+      <c r="O25" s="4">
+        <v>100</v>
+      </c>
+      <c r="P25" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -1994,9 +2048,15 @@
       <c r="M26" s="1">
         <v>114</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="1"/>
+      <c r="N26" s="3">
+        <v>45997</v>
+      </c>
+      <c r="O26" s="4">
+        <v>100</v>
+      </c>
+      <c r="P26" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -2038,9 +2098,15 @@
       <c r="M27" s="1">
         <v>115</v>
       </c>
-      <c r="N27" s="3"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="1"/>
+      <c r="N27" s="3">
+        <v>45997</v>
+      </c>
+      <c r="O27" s="4">
+        <v>100</v>
+      </c>
+      <c r="P27" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -2082,9 +2148,15 @@
       <c r="M28" s="1">
         <v>116</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="1"/>
+      <c r="N28" s="3">
+        <v>45997</v>
+      </c>
+      <c r="O28" s="4">
+        <v>100</v>
+      </c>
+      <c r="P28" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
@@ -2126,9 +2198,15 @@
       <c r="M29" s="1">
         <v>117</v>
       </c>
-      <c r="N29" s="3"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="1"/>
+      <c r="N29" s="3">
+        <v>45997</v>
+      </c>
+      <c r="O29" s="4">
+        <v>100</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -2170,9 +2248,15 @@
       <c r="M30" s="1">
         <v>118</v>
       </c>
-      <c r="N30" s="3"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="1"/>
+      <c r="N30" s="3">
+        <v>45997</v>
+      </c>
+      <c r="O30" s="4">
+        <v>100</v>
+      </c>
+      <c r="P30" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">

--- a/LoanOfficer-A/2023/130 kiranmala.xlsx
+++ b/LoanOfficer-A/2023/130 kiranmala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>11800</v>
+        <v>12000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -2298,9 +2298,15 @@
       <c r="M31" s="1">
         <v>119</v>
       </c>
-      <c r="N31" s="3"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="1"/>
+      <c r="N31" s="3">
+        <v>46006</v>
+      </c>
+      <c r="O31" s="4">
+        <v>100</v>
+      </c>
+      <c r="P31" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
@@ -2342,9 +2348,15 @@
       <c r="M32" s="1">
         <v>120</v>
       </c>
-      <c r="N32" s="3"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="1"/>
+      <c r="N32" s="3">
+        <v>46006</v>
+      </c>
+      <c r="O32" s="4">
+        <v>100</v>
+      </c>
+      <c r="P32" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
